--- a/vtesitaly/assets/archon/archon.xlsx
+++ b/vtesitaly/assets/archon/archon.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>#</t>
   </si>
@@ -25,81 +25,6 @@
   </si>
   <si>
     <t>Table#</t>
-  </si>
-  <si>
-    <t>Edouard</t>
-  </si>
-  <si>
-    <t>Menneson</t>
-  </si>
-  <si>
-    <t>Petr</t>
-  </si>
-  <si>
-    <t>Muller</t>
-  </si>
-  <si>
-    <t>Gianluca</t>
-  </si>
-  <si>
-    <t>Barzaghi</t>
-  </si>
-  <si>
-    <t>Frederic</t>
-  </si>
-  <si>
-    <t>Pin</t>
-  </si>
-  <si>
-    <t>Tero</t>
-  </si>
-  <si>
-    <t>Aalto</t>
-  </si>
-  <si>
-    <t>Matteo</t>
-  </si>
-  <si>
-    <t>Falsetti</t>
-  </si>
-  <si>
-    <t>Diego</t>
-  </si>
-  <si>
-    <t>DiNicolantonio</t>
-  </si>
-  <si>
-    <t>Giulio</t>
-  </si>
-  <si>
-    <t>Roffi</t>
-  </si>
-  <si>
-    <t>Nicola</t>
-  </si>
-  <si>
-    <t>Pampaloni</t>
-  </si>
-  <si>
-    <t>Ben</t>
-  </si>
-  <si>
-    <t>Fox</t>
-  </si>
-  <si>
-    <t>Paolo</t>
-  </si>
-  <si>
-    <t>Centis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">De Cicco</t>
-  </si>
-  <si>
-    <t>Tommaso</t>
-  </si>
-  <si>
-    <t>Chiodi</t>
   </si>
 </sst>
 </file>
@@ -663,192 +588,418 @@
       </c>
     </row>
     <row r="2" ht="14.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1">
-        <v>1</v>
-      </c>
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
     </row>
     <row r="3" ht="14.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="1">
-        <v>1</v>
-      </c>
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
     </row>
     <row r="4" ht="14.25">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="1">
-        <v>1</v>
-      </c>
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
     </row>
     <row r="5" ht="14.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="1">
-        <v>1</v>
-      </c>
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
     </row>
     <row r="6" ht="14.25">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
     </row>
     <row r="7" ht="14.25">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="1">
-        <v>2</v>
-      </c>
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
     </row>
     <row r="8" ht="14.25">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="1">
-        <v>2</v>
-      </c>
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
     </row>
     <row r="9" ht="14.25">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="1">
-        <v>2</v>
-      </c>
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
     </row>
     <row r="10" ht="14.25">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="1">
-        <v>2</v>
-      </c>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
     </row>
     <row r="11" ht="14.25">
-      <c r="A11" s="1">
-        <v>11</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="1">
-        <v>3</v>
-      </c>
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
     </row>
     <row r="12" ht="14.25">
-      <c r="A12" s="1">
-        <v>12</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="1">
-        <v>3</v>
-      </c>
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
     </row>
     <row r="13" ht="14.25">
-      <c r="A13" s="1">
-        <v>13</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" s="1">
-        <v>3</v>
-      </c>
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
     </row>
     <row r="14" ht="14.25">
-      <c r="A14" s="1">
-        <v>14</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" s="1">
-        <v>3</v>
-      </c>
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" ht="14.25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
     </row>
     <row r="16" ht="14.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
+    </row>
+    <row r="17" ht="14.25">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+    </row>
+    <row r="18" ht="14.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+    </row>
+    <row r="19" ht="14.25">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+    </row>
+    <row r="20" ht="14.25">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+    </row>
+    <row r="21" ht="14.25">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+    </row>
+    <row r="22" ht="14.25">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+    </row>
+    <row r="23" ht="14.25">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+    </row>
+    <row r="24" ht="14.25">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+    </row>
+    <row r="25" ht="14.25">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+    </row>
+    <row r="26" ht="14.25">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+    </row>
+    <row r="27" ht="14.25">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+    </row>
+    <row r="28" ht="14.25">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+    </row>
+    <row r="29" ht="14.25">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+    </row>
+    <row r="30" ht="14.25">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+    </row>
+    <row r="31" ht="14.25">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+    </row>
+    <row r="32" ht="14.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+    </row>
+    <row r="33" ht="14.25">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+    </row>
+    <row r="34" ht="14.25">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+    </row>
+    <row r="35" ht="14.25">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+    </row>
+    <row r="36" ht="14.25">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+    </row>
+    <row r="37" ht="14.25">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+    </row>
+    <row r="38" ht="14.25">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+    </row>
+    <row r="39" ht="14.25">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+    </row>
+    <row r="40" ht="14.25">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+    </row>
+    <row r="41" ht="14.25">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+    </row>
+    <row r="42" ht="14.25">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+    </row>
+    <row r="43" ht="14.25">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+    </row>
+    <row r="44" ht="14.25">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+    </row>
+    <row r="45" ht="14.25">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+    </row>
+    <row r="46" ht="14.25">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+    </row>
+    <row r="47" ht="14.25">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+    </row>
+    <row r="48" ht="14.25">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+    </row>
+    <row r="49" ht="14.25">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+    </row>
+    <row r="50" ht="14.25">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+    </row>
+    <row r="51" ht="14.25">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+    </row>
+    <row r="52" ht="14.25">
+      <c r="A52" s="1"/>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+    </row>
+    <row r="53" ht="14.25">
+      <c r="A53" s="1"/>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+    </row>
+    <row r="54" ht="14.25">
+      <c r="A54" s="1"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+    </row>
+    <row r="55" ht="14.25">
+      <c r="A55" s="1"/>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+    </row>
+    <row r="56" ht="14.25">
+      <c r="A56" s="1"/>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+    </row>
+    <row r="57" ht="14.25">
+      <c r="A57" s="1"/>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+    </row>
+    <row r="58" ht="14.25">
+      <c r="A58" s="1"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+    </row>
+    <row r="59" ht="14.25">
+      <c r="A59" s="1"/>
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+    </row>
+    <row r="60" ht="14.25">
+      <c r="A60" s="1"/>
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+    </row>
+    <row r="61" ht="14.25">
+      <c r="A61" s="1"/>
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+    </row>
+    <row r="62" ht="14.25">
+      <c r="A62" s="1"/>
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+    </row>
+    <row r="63" ht="14.25">
+      <c r="A63" s="1"/>
+      <c r="B63" s="1"/>
+      <c r="C63" s="1"/>
+      <c r="D63" s="1"/>
+    </row>
+    <row r="64" ht="14.25">
+      <c r="A64" s="1"/>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+    </row>
+    <row r="65" ht="14.25">
+      <c r="A65" s="1"/>
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+    </row>
+    <row r="66" ht="14.25">
+      <c r="A66" s="1"/>
+      <c r="B66" s="1"/>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+    </row>
+    <row r="67" ht="14.25">
+      <c r="A67" s="1"/>
+      <c r="B67" s="1"/>
+      <c r="C67" s="1"/>
+      <c r="D67" s="1"/>
+    </row>
+    <row r="68" ht="14.25">
+      <c r="A68" s="1"/>
+      <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+    </row>
+    <row r="69" ht="14.25">
+      <c r="A69" s="1"/>
+      <c r="B69" s="1"/>
+      <c r="C69" s="1"/>
+      <c r="D69" s="1"/>
+    </row>
+    <row r="70" ht="14.25">
+      <c r="A70" s="1"/>
+      <c r="B70" s="1"/>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>

--- a/vtesitaly/assets/archon/archon.xlsx
+++ b/vtesitaly/assets/archon/archon.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>#</t>
   </si>
@@ -25,6 +25,51 @@
   </si>
   <si>
     <t>Table#</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Francesco</t>
+  </si>
+  <si>
+    <t>Rampionesi</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Simone</t>
+  </si>
+  <si>
+    <t>Parmeggiani</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Lovre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De Grisogono</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Miro</t>
+  </si>
+  <si>
+    <t>Albertazzi</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Stefano</t>
+  </si>
+  <si>
+    <t>Chiodi</t>
   </si>
 </sst>
 </file>
@@ -570,7 +615,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="4" style="1" width="9.140625"/>
+    <col min="1" max="1" style="1" width="9.140625"/>
+    <col customWidth="1" min="2" max="2" style="1" width="11.421875"/>
+    <col customWidth="1" min="3" max="3" style="1" width="12.7109375"/>
+    <col min="4" max="4" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
@@ -588,34 +636,74 @@
       </c>
     </row>
     <row r="2" ht="14.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="3" ht="14.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="4" ht="14.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="5" ht="14.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="6" ht="14.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="7" ht="14.25">
       <c r="A7" s="1"/>

--- a/vtesitaly/assets/archon/archon.xlsx
+++ b/vtesitaly/assets/archon/archon.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="197">
   <si>
     <t>#</t>
   </si>
@@ -33,43 +33,577 @@
     <t>Francesco</t>
   </si>
   <si>
+    <t xml:space="preserve">La Rosa</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Petr</t>
+  </si>
+  <si>
+    <t>Muller</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Menneson</t>
+  </si>
+  <si>
+    <t>Edouard</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Thomas</t>
+  </si>
+  <si>
+    <t>Marchiori</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Filippo</t>
+  </si>
+  <si>
+    <t>Tomov</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Marco</t>
+  </si>
+  <si>
+    <t>Lombardo</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Niccolò</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Da Ronco</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Lovre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De Grisogono</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Federico</t>
+  </si>
+  <si>
+    <t>Ferrarini</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Adriano</t>
+  </si>
+  <si>
+    <t>Arena</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
     <t>Rampionesi</t>
   </si>
   <si>
-    <t>2</t>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Matteo</t>
+  </si>
+  <si>
+    <t>Sandrin</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Sven</t>
+  </si>
+  <si>
+    <t>Helmer</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>Carlos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lucas Acosta</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>Luca</t>
+  </si>
+  <si>
+    <t>Ruffoli</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>Stefano</t>
+  </si>
+  <si>
+    <t>Tarozzi</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Manfredini</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>Paolo</t>
+  </si>
+  <si>
+    <t>Pasqualin</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>Diego</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Di Nicolantonio</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Ivan</t>
+  </si>
+  <si>
+    <t>Candioli</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>Nicola</t>
+  </si>
+  <si>
+    <t>Pampaloni</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>Mengoli</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Pirera</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>Enrico</t>
+  </si>
+  <si>
+    <t>Bertusi</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>Martin</t>
+  </si>
+  <si>
+    <t>Weinmayer</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Alessio</t>
+  </si>
+  <si>
+    <t>Camola</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Alessandro</t>
+  </si>
+  <si>
+    <t>Aprigliano</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>Tero</t>
+  </si>
+  <si>
+    <t>Aalto</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>Carlo</t>
+  </si>
+  <si>
+    <t>Lorenzetti</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Fabio</t>
+  </si>
+  <si>
+    <t>Laviosa</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>Damiano</t>
+  </si>
+  <si>
+    <t>Ghiaroni</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>Tommaso</t>
+  </si>
+  <si>
+    <t>Chiodi</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>Massimo</t>
+  </si>
+  <si>
+    <t>Vaccari</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>Dean</t>
+  </si>
+  <si>
+    <t>Garratt</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>Gianluca</t>
+  </si>
+  <si>
+    <t>Barzaghi</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>Ruben</t>
+  </si>
+  <si>
+    <t>Feldman</t>
+  </si>
+  <si>
+    <t>37</t>
   </si>
   <si>
     <t>Simone</t>
   </si>
   <si>
-    <t>Parmeggiani</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Lovre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">De Grisogono</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Miro</t>
-  </si>
-  <si>
-    <t>Albertazzi</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Stefano</t>
-  </si>
-  <si>
-    <t>Chiodi</t>
+    <t>Zanni</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>Laurent</t>
+  </si>
+  <si>
+    <t>Ribeyre</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>Leonardo</t>
+  </si>
+  <si>
+    <t>Magri</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>Gaspar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vaquer Gómez</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>Bensi</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>Marini</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>Centis</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>Barletti</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>Frederic</t>
+  </si>
+  <si>
+    <t>Pin</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>Jean-Baptiste</t>
+  </si>
+  <si>
+    <t>Becker</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>Ben</t>
+  </si>
+  <si>
+    <t>Fox</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>Cristiano</t>
+  </si>
+  <si>
+    <t>Fossi</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>Raffaele</t>
+  </si>
+  <si>
+    <t>Gallotta</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>Donati</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>Giovanni</t>
+  </si>
+  <si>
+    <t>Gueli</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>Dominik</t>
+  </si>
+  <si>
+    <t>Trupcevic</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>Danilo</t>
+  </si>
+  <si>
+    <t>Fruttaldo</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De Stefano</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>Roncaglia</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>Andrea</t>
+  </si>
+  <si>
+    <t>Piserchia</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>Giulio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">De Cicco</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>Roffi</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>Pablo</t>
+  </si>
+  <si>
+    <t>Carnino</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>Ferrari</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>Turicchi</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>Lonardi</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>Lorand</t>
+  </si>
+  <si>
+    <t>Lionel</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>Torrisi</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>Lorenzo</t>
+  </si>
+  <si>
+    <t>Ferri</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>Falsetti</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>Arturo</t>
+  </si>
+  <si>
+    <t>Parise</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>Danny</t>
+  </si>
+  <si>
+    <t>Buset</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>Riccardo</t>
+  </si>
+  <si>
+    <t>Biscontin</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>Paderni</t>
   </si>
 </sst>
 </file>
@@ -104,8 +638,9 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -706,328 +1241,760 @@
       </c>
     </row>
     <row r="7" ht="14.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
+      <c r="A7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="8" ht="14.25">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="9" ht="14.25">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
+      <c r="A9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="10" ht="14.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
+      <c r="A10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="11" ht="14.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
+      <c r="A11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="12" ht="14.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
+      <c r="A12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="13" ht="14.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+      <c r="A13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="14" ht="14.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
+      <c r="A14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="15" ht="14.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
+      <c r="A15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="16" ht="14.25">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
+      <c r="A16" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="17" ht="14.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
+      <c r="A17" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="18" ht="14.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
+      <c r="A18" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="19" ht="14.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
+      <c r="A19" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="20" ht="14.25">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
+      <c r="A20" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="21" ht="14.25">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
+      <c r="A21" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="22" ht="14.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
+      <c r="A22" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="23" ht="14.25">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
+      <c r="A23" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="24" ht="14.25">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
+      <c r="A24" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="25" ht="14.25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
+      <c r="A25" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="26" ht="14.25">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
+      <c r="A26" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="27" ht="14.25">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
+      <c r="A27" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="28" ht="14.25">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
+      <c r="A28" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="29" ht="14.25">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
+      <c r="A29" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="30" ht="14.25">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
+      <c r="A30" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="31" ht="14.25">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
+      <c r="A31" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="32" ht="14.25">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
+      <c r="A32" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="33" ht="14.25">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
+      <c r="A33" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="34" ht="14.25">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
+      <c r="A34" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="35" ht="14.25">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
+      <c r="A35" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="36" ht="14.25">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
+      <c r="A36" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="37" ht="14.25">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
+      <c r="A37" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="38" ht="14.25">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
+      <c r="A38" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="39" ht="14.25">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
+      <c r="A39" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="40" ht="14.25">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
+      <c r="A40" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="41" ht="14.25">
-      <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
+      <c r="A41" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="42" ht="14.25">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
+      <c r="A42" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="43" ht="14.25">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
+      <c r="A43" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="44" ht="14.25">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
+      <c r="A44" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="45" ht="14.25">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
+      <c r="A45" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="46" ht="14.25">
-      <c r="A46" s="1"/>
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
+      <c r="A46" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="47" ht="14.25">
-      <c r="A47" s="1"/>
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
+      <c r="A47" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="48" ht="14.25">
-      <c r="A48" s="1"/>
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
+      <c r="A48" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="49" ht="14.25">
-      <c r="A49" s="1"/>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
+      <c r="A49" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="50" ht="14.25">
-      <c r="A50" s="1"/>
-      <c r="B50" s="1"/>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
+      <c r="A50" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="51" ht="14.25">
-      <c r="A51" s="1"/>
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
+      <c r="A51" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="52" ht="14.25">
-      <c r="A52" s="1"/>
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
+      <c r="A52" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="53" ht="14.25">
-      <c r="A53" s="1"/>
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
-      <c r="D53" s="1"/>
+      <c r="A53" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="54" ht="14.25">
-      <c r="A54" s="1"/>
-      <c r="B54" s="1"/>
-      <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
+      <c r="A54" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="55" ht="14.25">
-      <c r="A55" s="1"/>
-      <c r="B55" s="1"/>
-      <c r="C55" s="1"/>
-      <c r="D55" s="1"/>
+      <c r="A55" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="56" ht="14.25">
-      <c r="A56" s="1"/>
-      <c r="B56" s="1"/>
-      <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
+      <c r="A56" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="57" ht="14.25">
-      <c r="A57" s="1"/>
-      <c r="B57" s="1"/>
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
+      <c r="A57" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="58" ht="14.25">
-      <c r="A58" s="1"/>
-      <c r="B58" s="1"/>
-      <c r="C58" s="1"/>
-      <c r="D58" s="1"/>
+      <c r="A58" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="59" ht="14.25">
-      <c r="A59" s="1"/>
-      <c r="B59" s="1"/>
-      <c r="C59" s="1"/>
-      <c r="D59" s="1"/>
+      <c r="A59" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="60" ht="14.25">
-      <c r="A60" s="1"/>
-      <c r="B60" s="1"/>
-      <c r="C60" s="1"/>
-      <c r="D60" s="1"/>
+      <c r="A60" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="61" ht="14.25">
       <c r="A61" s="1"/>
@@ -1036,28 +2003,60 @@
       <c r="D61" s="1"/>
     </row>
     <row r="62" ht="14.25">
-      <c r="A62" s="1"/>
-      <c r="B62" s="1"/>
-      <c r="C62" s="1"/>
-      <c r="D62" s="1"/>
+      <c r="A62" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="63" ht="14.25">
-      <c r="A63" s="1"/>
-      <c r="B63" s="1"/>
-      <c r="C63" s="1"/>
-      <c r="D63" s="1"/>
+      <c r="A63" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="64" ht="14.25">
-      <c r="A64" s="1"/>
-      <c r="B64" s="1"/>
-      <c r="C64" s="1"/>
-      <c r="D64" s="1"/>
+      <c r="A64" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="65" ht="14.25">
-      <c r="A65" s="1"/>
-      <c r="B65" s="1"/>
-      <c r="C65" s="1"/>
-      <c r="D65" s="1"/>
+      <c r="A65" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="66" ht="14.25">
       <c r="A66" s="1"/>
@@ -1066,28 +2065,122 @@
       <c r="D66" s="1"/>
     </row>
     <row r="67" ht="14.25">
-      <c r="A67" s="1"/>
-      <c r="B67" s="1"/>
-      <c r="C67" s="1"/>
-      <c r="D67" s="1"/>
+      <c r="A67" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="68" ht="14.25">
-      <c r="A68" s="1"/>
-      <c r="B68" s="1"/>
-      <c r="C68" s="1"/>
-      <c r="D68" s="1"/>
+      <c r="A68" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="69" ht="14.25">
-      <c r="A69" s="1"/>
-      <c r="B69" s="1"/>
-      <c r="C69" s="1"/>
-      <c r="D69" s="1"/>
+      <c r="A69" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="70" ht="14.25">
-      <c r="A70" s="1"/>
-      <c r="B70" s="1"/>
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
+      <c r="A70" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="71" ht="14.25">
+      <c r="A71" s="1"/>
+      <c r="B71" s="1"/>
+      <c r="C71" s="1"/>
+      <c r="D71" s="1"/>
+    </row>
+    <row r="72" ht="14.25">
+      <c r="A72" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="73" ht="14.25">
+      <c r="A73" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="74" ht="14.25">
+      <c r="A74" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="75" ht="14.25">
+      <c r="A75" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>45</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>

--- a/vtesitaly/assets/archon/archon.xlsx
+++ b/vtesitaly/assets/archon/archon.xlsx
@@ -3,17 +3,18 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Round 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Standings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="273">
   <si>
     <t>#</t>
   </si>
@@ -604,6 +605,234 @@
   </si>
   <si>
     <t>Paderni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final Rank</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prelim GWs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prelim VPs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final VPs</t>
+  </si>
+  <si>
+    <t>TPs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frederic Pin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federico Ferrarini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Danilo Torrisi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ruben Feldman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicola Pampaloni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enrico De Stefano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leonardo Bensi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martin Weinmayer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Danny Buset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Marchiori</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lorand Lionel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andrea Paderni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diego Di Nicolantonio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arturo Parise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gianluca Barzaghi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laurent Ribeyre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enrico Bertusi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Giulio De Cicco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luca Manfredini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niccolò Da Ronco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simone Zanni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alessandro Donati</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paolo Pasqualin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paolo Centis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Francesco La Rosa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pablo Carnino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stefano Chiodi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberto Giampaolo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicola Lonardi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dean Garratt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gaspar Vaquer Gómez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gianluca Marini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matteo Sandrin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cristiano Fossi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filippo Mengoli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matteo Falsetti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marco Lombardo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leonardo Barletti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Francesco Rampionesi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filippo Tomov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lovre De Grisogono</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carlos Lucas Acosta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sven Helmer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luca Ruffoli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luca Turicchi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menneson Edouard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alessio Camola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leonardo Magri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raffaele Gallotta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabio Laviosa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lorenzo Ferri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stefano Tarozzi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alessandro Roncaglia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andrea Piserchia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben Fox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alessandro Aprigliano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matteo Ferrari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Danilo Fruttaldo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adriano Arena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massimo Vaccari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ivan Candioli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Giovanni Gueli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jean-Baptiste Becker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Giulio Roffi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Damiano Ghiaroni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carlo Lorenzetti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dominik Trupcevic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tommaso Chiodi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicola Pirera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petr Muller</t>
   </si>
 </sst>
 </file>
@@ -638,9 +867,8 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1241,72 +1469,72 @@
       </c>
     </row>
     <row r="7" ht="14.25">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" ht="14.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9" ht="14.25">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="10" ht="14.25">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" ht="14.25">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2180,6 +2408,1308 @@
       </c>
       <c r="D75" s="1" t="s">
         <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData>
+    <row r="1" ht="14.25">
+      <c r="A1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E1" t="s">
+        <v>201</v>
+      </c>
+      <c r="F1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="2" ht="14.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>9</v>
+      </c>
+      <c r="E2">
+        <v>1.5</v>
+      </c>
+      <c r="F2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="3" ht="14.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>9.5</v>
+      </c>
+      <c r="E3">
+        <v>0.5</v>
+      </c>
+      <c r="F3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>7.5</v>
+      </c>
+      <c r="E4">
+        <v>0.5</v>
+      </c>
+      <c r="F4">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>206</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>10</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>207</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>8</v>
+      </c>
+      <c r="E6">
+        <v>0.5</v>
+      </c>
+      <c r="F6">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>208</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>7.5</v>
+      </c>
+      <c r="E7"/>
+      <c r="F7">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>209</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>6</v>
+      </c>
+      <c r="E8"/>
+      <c r="F8">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>210</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>7</v>
+      </c>
+      <c r="E9"/>
+      <c r="F9">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>211</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>7</v>
+      </c>
+      <c r="E10"/>
+      <c r="F10">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>212</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>6.5</v>
+      </c>
+      <c r="E11"/>
+      <c r="F11">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>6</v>
+      </c>
+      <c r="E12"/>
+      <c r="F12">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>214</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>6</v>
+      </c>
+      <c r="E13"/>
+      <c r="F13">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>215</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>6</v>
+      </c>
+      <c r="E14"/>
+      <c r="F14">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>216</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>5</v>
+      </c>
+      <c r="E15"/>
+      <c r="F15">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>217</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>5</v>
+      </c>
+      <c r="E16"/>
+      <c r="F16">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>218</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>4.5</v>
+      </c>
+      <c r="E17"/>
+      <c r="F17">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>219</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>4.5</v>
+      </c>
+      <c r="E18"/>
+      <c r="F18">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>220</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>4.5</v>
+      </c>
+      <c r="E19"/>
+      <c r="F19">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>221</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>4</v>
+      </c>
+      <c r="E20"/>
+      <c r="F20">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>222</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>4</v>
+      </c>
+      <c r="E21"/>
+      <c r="F21">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>223</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>4</v>
+      </c>
+      <c r="E22"/>
+      <c r="F22">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>224</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>4</v>
+      </c>
+      <c r="E23"/>
+      <c r="F23">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>225</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>3.5</v>
+      </c>
+      <c r="E24"/>
+      <c r="F24">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>226</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>3</v>
+      </c>
+      <c r="E25"/>
+      <c r="F25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>227</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>3.5</v>
+      </c>
+      <c r="E26"/>
+      <c r="F26">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>228</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>3.5</v>
+      </c>
+      <c r="E27"/>
+      <c r="F27">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="28" ht="14.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>229</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>3</v>
+      </c>
+      <c r="E28"/>
+      <c r="F28">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="29" ht="14.25">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>230</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>3</v>
+      </c>
+      <c r="E29"/>
+      <c r="F29">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="30" ht="14.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>231</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>3</v>
+      </c>
+      <c r="E30"/>
+      <c r="F30">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="31" ht="14.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>232</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>2.5</v>
+      </c>
+      <c r="E31"/>
+      <c r="F31">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="32" ht="14.25">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>233</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>2.5</v>
+      </c>
+      <c r="E32"/>
+      <c r="F32">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="33" ht="14.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>234</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>2</v>
+      </c>
+      <c r="E33"/>
+      <c r="F33">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="34" ht="14.25">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34" t="s">
+        <v>235</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>2</v>
+      </c>
+      <c r="E34"/>
+      <c r="F34">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="35" ht="14.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>236</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>2</v>
+      </c>
+      <c r="E35"/>
+      <c r="F35">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="36" ht="14.25">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36" t="s">
+        <v>237</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <v>2</v>
+      </c>
+      <c r="E36"/>
+      <c r="F36">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="37" ht="14.25">
+      <c r="A37">
+        <v>34</v>
+      </c>
+      <c r="B37" t="s">
+        <v>238</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37">
+        <v>2</v>
+      </c>
+      <c r="E37"/>
+      <c r="F37">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="38" ht="14.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>239</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>2</v>
+      </c>
+      <c r="E38"/>
+      <c r="F38">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="39" ht="14.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>240</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <v>2</v>
+      </c>
+      <c r="E39"/>
+      <c r="F39">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="40" ht="14.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>241</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+      <c r="D40">
+        <v>1.5</v>
+      </c>
+      <c r="E40"/>
+      <c r="F40">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="41" ht="14.25">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41" t="s">
+        <v>242</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>1.5</v>
+      </c>
+      <c r="E41"/>
+      <c r="F41">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="42" ht="14.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>243</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="D42">
+        <v>1.5</v>
+      </c>
+      <c r="E42"/>
+      <c r="F42">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="43" ht="14.25">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43" t="s">
+        <v>244</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <v>1.5</v>
+      </c>
+      <c r="E43"/>
+      <c r="F43">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="44" ht="14.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>245</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44"/>
+      <c r="F44">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="45" ht="14.25">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45" t="s">
+        <v>246</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45"/>
+      <c r="F45">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="46" ht="14.25">
+      <c r="A46">
+        <v>43</v>
+      </c>
+      <c r="B46" t="s">
+        <v>247</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="E46"/>
+      <c r="F46">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="47" ht="14.25">
+      <c r="A47">
+        <v>43</v>
+      </c>
+      <c r="B47" t="s">
+        <v>248</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>1</v>
+      </c>
+      <c r="E47"/>
+      <c r="F47">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="48" ht="14.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>249</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <v>1</v>
+      </c>
+      <c r="E48"/>
+      <c r="F48">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="49" ht="14.25">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49" t="s">
+        <v>250</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <v>1</v>
+      </c>
+      <c r="E49"/>
+      <c r="F49">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="50" ht="14.25">
+      <c r="A50">
+        <v>47</v>
+      </c>
+      <c r="B50" t="s">
+        <v>251</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+      <c r="D50">
+        <v>1</v>
+      </c>
+      <c r="E50"/>
+      <c r="F50">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="51" ht="14.25">
+      <c r="A51">
+        <v>47</v>
+      </c>
+      <c r="B51" t="s">
+        <v>252</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+      <c r="D51">
+        <v>1</v>
+      </c>
+      <c r="E51"/>
+      <c r="F51">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="52" ht="14.25">
+      <c r="A52">
+        <v>47</v>
+      </c>
+      <c r="B52" t="s">
+        <v>253</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
+      <c r="E52"/>
+      <c r="F52">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="53" ht="14.25">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>254</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+      <c r="D53">
+        <v>1</v>
+      </c>
+      <c r="E53"/>
+      <c r="F53">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="54" ht="14.25">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="B54" t="s">
+        <v>255</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54">
+        <v>1</v>
+      </c>
+      <c r="E54"/>
+      <c r="F54">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="55" ht="14.25">
+      <c r="A55">
+        <v>52</v>
+      </c>
+      <c r="B55" t="s">
+        <v>256</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="D55">
+        <v>1</v>
+      </c>
+      <c r="E55"/>
+      <c r="F55">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="56" ht="14.25">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>257</v>
+      </c>
+      <c r="C56">
+        <v>0</v>
+      </c>
+      <c r="D56">
+        <v>1</v>
+      </c>
+      <c r="E56"/>
+      <c r="F56">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="57" ht="14.25">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="B57" t="s">
+        <v>258</v>
+      </c>
+      <c r="C57">
+        <v>0</v>
+      </c>
+      <c r="D57">
+        <v>1</v>
+      </c>
+      <c r="E57"/>
+      <c r="F57">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="58" ht="14.25">
+      <c r="A58">
+        <v>55</v>
+      </c>
+      <c r="B58" t="s">
+        <v>259</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+      <c r="D58">
+        <v>1</v>
+      </c>
+      <c r="E58"/>
+      <c r="F58">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="59" ht="14.25">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>260</v>
+      </c>
+      <c r="C59">
+        <v>0</v>
+      </c>
+      <c r="D59">
+        <v>0.5</v>
+      </c>
+      <c r="E59"/>
+      <c r="F59">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="60" ht="14.25">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>261</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60"/>
+      <c r="F60">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="61" ht="14.25">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>262</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+      <c r="E61"/>
+      <c r="F61">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="62" ht="14.25">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="B62" t="s">
+        <v>263</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62">
+        <v>0</v>
+      </c>
+      <c r="E62"/>
+      <c r="F62">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="63" ht="14.25">
+      <c r="A63">
+        <v>60</v>
+      </c>
+      <c r="B63" t="s">
+        <v>264</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+      <c r="E63"/>
+      <c r="F63">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="64" ht="14.25">
+      <c r="A64">
+        <v>60</v>
+      </c>
+      <c r="B64" t="s">
+        <v>265</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64"/>
+      <c r="F64">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="65" ht="14.25">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>266</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65"/>
+      <c r="F65">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="66" ht="14.25">
+      <c r="A66">
+        <v>64</v>
+      </c>
+      <c r="B66" t="s">
+        <v>267</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+      <c r="E66"/>
+      <c r="F66">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="67" ht="14.25">
+      <c r="A67">
+        <v>64</v>
+      </c>
+      <c r="B67" t="s">
+        <v>268</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+      <c r="D67">
+        <v>0</v>
+      </c>
+      <c r="E67"/>
+      <c r="F67">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" ht="14.25">
+      <c r="A68">
+        <v>64</v>
+      </c>
+      <c r="B68" t="s">
+        <v>269</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68"/>
+      <c r="F68">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="69" ht="14.25">
+      <c r="A69">
+        <v>64</v>
+      </c>
+      <c r="B69" t="s">
+        <v>270</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+      <c r="E69"/>
+      <c r="F69">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="70" ht="14.25">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>271</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
+      <c r="D70">
+        <v>0</v>
+      </c>
+      <c r="E70"/>
+      <c r="F70">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="71" ht="14.25">
+      <c r="A71">
+        <v>69</v>
+      </c>
+      <c r="B71" t="s">
+        <v>272</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71">
+        <v>0</v>
+      </c>
+      <c r="E71"/>
+      <c r="F71">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
